--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -394,25 +394,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>920.25</v>
+        <v>920.6396999999999</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>937.02</v>
+        <v>936.22</v>
       </c>
       <c r="E2">
-        <v>651.4400000000001</v>
+        <v>651.61</v>
       </c>
       <c r="F2">
-        <v>290.39</v>
+        <v>290.35</v>
       </c>
       <c r="G2">
-        <v>1245.84</v>
+        <v>1245.59</v>
       </c>
     </row>
   </sheetData>
@@ -464,25 +464,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1020.15</v>
+        <v>949.66</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1044.56</v>
+        <v>936.26</v>
       </c>
       <c r="E2">
-        <v>714</v>
+        <v>675.9400000000001</v>
       </c>
       <c r="F2">
-        <v>319.6</v>
+        <v>309.59</v>
       </c>
       <c r="G2">
-        <v>1354.67</v>
+        <v>1267.63</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -352,67 +352,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost_per_year</t>
+          <t>mean_visits_cost</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_cost_per_year</t>
+          <t>min_visits_cost</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_cost_per_year</t>
+          <t>max_visits_cost</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_cost_per_year</t>
+          <t>sd_visits_cost</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_cost_per_year</t>
+          <t>median_visits_cost</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_cost_per_year</t>
+          <t>q1_visits_cost</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_cost_per_year</t>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>920.6396999999999</v>
+        <v>890.6</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>936.22</v>
+        <v>1028.79</v>
       </c>
       <c r="E2">
-        <v>651.61</v>
+        <v>561.59</v>
       </c>
       <c r="F2">
-        <v>290.35</v>
+        <v>187.2</v>
       </c>
       <c r="G2">
-        <v>1245.59</v>
+        <v>1218</v>
+      </c>
+      <c r="H2">
+        <v>17705</v>
+      </c>
+      <c r="I2">
+        <v>7.731767191089252</v>
+      </c>
+      <c r="J2">
+        <v>875.4449786704703</v>
+      </c>
+      <c r="K2">
+        <v>905.7550213295298</v>
       </c>
     </row>
   </sheetData>
@@ -422,67 +454,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mean_visit_cost</t>
+          <t>mean_visits_cost</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>min_visit_cost</t>
+          <t>min_visits_cost</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>max_visit_cost</t>
+          <t>max_visits_cost</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>sd_visit_cost</t>
+          <t>sd_visits_cost</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>median_visit_cost</t>
+          <t>median_visits_cost</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>lower_q_visits_cost</t>
+          <t>q1_visits_cost</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>upper_q_visits_cost</t>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>949.66</v>
+        <v>928.74</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>14098.5</v>
       </c>
       <c r="D2">
-        <v>936.26</v>
+        <v>1033.59</v>
       </c>
       <c r="E2">
-        <v>675.9400000000001</v>
+        <v>603.79</v>
       </c>
       <c r="F2">
-        <v>309.59</v>
+        <v>210</v>
       </c>
       <c r="G2">
-        <v>1267.63</v>
+        <v>1260</v>
+      </c>
+      <c r="H2">
+        <v>16978</v>
+      </c>
+      <c r="I2">
+        <v>7.932407824368062</v>
+      </c>
+      <c r="J2">
+        <v>913.1916578454712</v>
+      </c>
+      <c r="K2">
+        <v>944.2883421545288</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -414,37 +414,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>890.6</v>
+        <v>829.76</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1028.79</v>
+        <v>924.16</v>
       </c>
       <c r="E2">
-        <v>561.59</v>
+        <v>546</v>
       </c>
       <c r="F2">
-        <v>187.2</v>
+        <v>182.76</v>
       </c>
       <c r="G2">
-        <v>1218</v>
+        <v>1149.59</v>
       </c>
       <c r="H2">
         <v>17705</v>
       </c>
       <c r="I2">
-        <v>7.731767191089252</v>
+        <v>6.945431008580024</v>
       </c>
       <c r="J2">
-        <v>875.4449786704703</v>
+        <v>816.1462746411821</v>
       </c>
       <c r="K2">
-        <v>905.7550213295298</v>
+        <v>843.3737253588179</v>
       </c>
     </row>
   </sheetData>
@@ -516,37 +516,37 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>928.74</v>
+        <v>865.29</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
       <c r="C2">
-        <v>14098.5</v>
+        <v>14096</v>
       </c>
       <c r="D2">
-        <v>1033.59</v>
+        <v>927.3099999999999</v>
       </c>
       <c r="E2">
-        <v>603.79</v>
+        <v>584.39</v>
       </c>
       <c r="F2">
         <v>210</v>
       </c>
       <c r="G2">
-        <v>1260</v>
+        <v>1187.41</v>
       </c>
       <c r="H2">
         <v>16978</v>
       </c>
       <c r="I2">
-        <v>7.932407824368062</v>
+        <v>7.116749484432655</v>
       </c>
       <c r="J2">
-        <v>913.1916578454712</v>
+        <v>851.3404327989666</v>
       </c>
       <c r="K2">
-        <v>944.2883421545288</v>
+        <v>879.2395672010333</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -414,7 +414,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>829.76</v>
+        <v>913.63</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -423,28 +423,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>924.16</v>
+        <v>932.5700000000001</v>
       </c>
       <c r="E2">
-        <v>546</v>
+        <v>641.5</v>
       </c>
       <c r="F2">
-        <v>182.76</v>
+        <v>278.75</v>
       </c>
       <c r="G2">
-        <v>1149.59</v>
+        <v>1234.54</v>
       </c>
       <c r="H2">
-        <v>17705</v>
+        <v>22900</v>
       </c>
       <c r="I2">
-        <v>6.945431008580024</v>
+        <v>6.16259602226403</v>
       </c>
       <c r="J2">
-        <v>816.1462746411821</v>
+        <v>901.5508952845106</v>
       </c>
       <c r="K2">
-        <v>843.3737253588179</v>
+        <v>925.7091047154894</v>
       </c>
     </row>
   </sheetData>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>865.29</v>
+        <v>939.1</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -525,28 +525,28 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>927.3099999999999</v>
+        <v>932.75</v>
       </c>
       <c r="E2">
-        <v>584.39</v>
+        <v>672</v>
       </c>
       <c r="F2">
-        <v>210</v>
+        <v>294</v>
       </c>
       <c r="G2">
-        <v>1187.41</v>
+        <v>1260</v>
       </c>
       <c r="H2">
-        <v>16978</v>
+        <v>22279</v>
       </c>
       <c r="I2">
-        <v>7.116749484432655</v>
+        <v>6.249099086735912</v>
       </c>
       <c r="J2">
-        <v>851.3404327989666</v>
+        <v>926.8513253837681</v>
       </c>
       <c r="K2">
-        <v>879.2395672010333</v>
+        <v>951.348674616232</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -1,22 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_7260D3E18BFC11AFA8E6447C63D9BA9B8E19C014" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="unadjusted_all_costs_summary" sheetId="1" r:id="rId1"/>
     <sheet name="unadjusted_user_only_costs" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+  <si>
+    <t>mean_visits_cost</t>
+  </si>
+  <si>
+    <t>min_visits_cost</t>
+  </si>
+  <si>
+    <t>max_visits_cost</t>
+  </si>
+  <si>
+    <t>sd_visits_cost</t>
+  </si>
+  <si>
+    <t>median_visits_cost</t>
+  </si>
+  <si>
+    <t>q1_visits_cost</t>
+  </si>
+  <si>
+    <t>q3_visits_cost</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +108,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +160,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +194,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +229,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,68 +405,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_visits_cost</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>min_visits_cost</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>max_visits_cost</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd_visits_cost</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median_visits_cost</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>q1_visits_cost</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>q3_visits_cost</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>lower</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>upper</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>913.63</v>
       </c>
@@ -423,7 +455,7 @@
         <v>14096</v>
       </c>
       <c r="D2">
-        <v>932.5700000000001</v>
+        <v>932.57</v>
       </c>
       <c r="E2">
         <v>641.5</v>
@@ -438,13 +470,13 @@
         <v>22900</v>
       </c>
       <c r="I2">
-        <v>6.16259602226403</v>
+        <v>6.1625960222640304</v>
       </c>
       <c r="J2">
         <v>901.5508952845106</v>
       </c>
       <c r="K2">
-        <v>925.7091047154894</v>
+        <v>925.70910471548939</v>
       </c>
     </row>
   </sheetData>
@@ -453,68 +485,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>mean_visits_cost</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>min_visits_cost</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>max_visits_cost</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sd_visits_cost</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>median_visits_cost</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>q1_visits_cost</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>q3_visits_cost</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>lower</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>upper</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>939.1</v>
       </c>
@@ -543,10 +553,10 @@
         <v>6.249099086735912</v>
       </c>
       <c r="J2">
-        <v>926.8513253837681</v>
+        <v>926.85132538376808</v>
       </c>
       <c r="K2">
-        <v>951.348674616232</v>
+        <v>951.34867461623196</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP-Unadjusted.xlsx
@@ -1,66 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7260D3E18BFC11AFA8E6447C63D9BA9B8E19C014" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="unadjusted_all_costs_summary" sheetId="1" r:id="rId1"/>
     <sheet name="unadjusted_user_only_costs" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
-  <si>
-    <t>mean_visits_cost</t>
-  </si>
-  <si>
-    <t>min_visits_cost</t>
-  </si>
-  <si>
-    <t>max_visits_cost</t>
-  </si>
-  <si>
-    <t>sd_visits_cost</t>
-  </si>
-  <si>
-    <t>median_visits_cost</t>
-  </si>
-  <si>
-    <t>q1_visits_cost</t>
-  </si>
-  <si>
-    <t>q3_visits_cost</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>se</t>
-  </si>
-  <si>
-    <t>lower</t>
-  </si>
-  <si>
-    <t>upper</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -194,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -229,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -405,78 +351,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_cost</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visits_cost</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visits_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visits_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visits_cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>q1_visits_cost</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2">
-        <v>913.63</v>
+        <v>3944.4</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>81673.47</v>
       </c>
       <c r="D2">
-        <v>932.57</v>
+        <v>4327.01</v>
       </c>
       <c r="E2">
-        <v>641.5</v>
+        <v>2665.56</v>
       </c>
       <c r="F2">
-        <v>278.75</v>
+        <v>1095.92</v>
       </c>
       <c r="G2">
-        <v>1234.54</v>
+        <v>5302.35</v>
       </c>
       <c r="H2">
         <v>22900</v>
       </c>
       <c r="I2">
-        <v>6.1625960222640304</v>
+        <v>28.59368692355178</v>
       </c>
       <c r="J2">
-        <v>901.5508952845106</v>
+        <v>3888.354441066118</v>
       </c>
       <c r="K2">
-        <v>925.70910471548939</v>
+        <v>4000.445558933882</v>
       </c>
     </row>
   </sheetData>
@@ -485,78 +453,100 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_cost</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visits_cost</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visits_cost</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visits_cost</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visits_cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>q1_visits_cost</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>q3_visits_cost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2">
-        <v>939.1</v>
+        <v>3598.47</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>1.65</v>
       </c>
       <c r="C2">
-        <v>14096</v>
+        <v>76184</v>
       </c>
       <c r="D2">
-        <v>932.75</v>
+        <v>3994.12</v>
       </c>
       <c r="E2">
-        <v>672</v>
+        <v>2397.71</v>
       </c>
       <c r="F2">
-        <v>294</v>
+        <v>1001.83</v>
       </c>
       <c r="G2">
-        <v>1260</v>
+        <v>4814.04</v>
       </c>
       <c r="H2">
-        <v>22279</v>
+        <v>22301</v>
       </c>
       <c r="I2">
-        <v>6.249099086735912</v>
+        <v>26.74600613540884</v>
       </c>
       <c r="J2">
-        <v>926.85132538376808</v>
+        <v>3546.04594585569</v>
       </c>
       <c r="K2">
-        <v>951.34867461623196</v>
+        <v>3650.894054144309</v>
       </c>
     </row>
   </sheetData>
